--- a/satisfaction_surveys/008_salary_survey_for_public_officials--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/008_salary_survey_for_public_officials--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_1</t>
+          <t>role_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your role?</t>
+          <t>What is your role in the public official position (job title)?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your salary range (per year)?</t>
+          <t>What is your annual salary range?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>survey_3</t>
+          <t>benefits_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are your benefits?</t>
+          <t>Do you have any benefits with your job?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>salary_4</t>
+          <t>satisfaction_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your salary range (per year)?</t>
+          <t>Are you satisfied with your current job?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>benefits_5</t>
+          <t>schedule_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are your benefits?</t>
+          <t>What is your typical work schedule like (hours worked per week)?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_6</t>
+          <t>day_at_work_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your job title/position?</t>
+          <t>Can you describe your typical day at work?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>survey_7</t>
+          <t>training_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Are you satisfied with your job?</t>
+          <t>What kind of training have you received for your job?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>role_8</t>
+          <t>experience_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your role?</t>
+          <t>How many years do you have of experience in this position?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_9</t>
+          <t>job_security_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your job title/position?</t>
+          <t>Do you feel your job is secure?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_10</t>
+          <t>work_life_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your job title/position?</t>
+          <t>Are you able to balance work and family life?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>stress_anxiety_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any job-related stress or anxiety?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>weeks_worked_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How many weeks do you work per year?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -781,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_1_choices</t>
+          <t>benefits_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -798,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_1_choices</t>
+          <t>benefits_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>salary_2_choices</t>
+          <t>satisfaction_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>salary_2_choices</t>
+          <t>satisfaction_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>survey_3_choices</t>
+          <t>training_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>survey_3_choices</t>
+          <t>training_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>salary_4_choices</t>
+          <t>job_security_9_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>salary_4_choices</t>
+          <t>job_security_9_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>benefits_5_choices</t>
+          <t>work_life_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -934,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>benefits_5_choices</t>
+          <t>work_life_10_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -951,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>survey_7_choices</t>
+          <t>stress_anxiety_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>survey_7_choices</t>
+          <t>stress_anxiety_11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -977,40 +1023,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>role_8_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>role_8_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
